--- a/data/trans_orig/P21D6_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D6_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitándolo, no pudo recibir atención fisioterapéutica en 2023</t>
+          <t>Población que, necesitándolo, no pudo recibir atención fisioterapéutica en 2023 (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>175072</t>
+          <t>174885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>200178</t>
+          <t>199138</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>177157</t>
+          <t>176679</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>193805</t>
+          <t>194597</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>358697</t>
+          <t>358708</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>389441</t>
+          <t>389290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,9%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19631</t>
+          <t>19279</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42908</t>
+          <t>42727</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21495</t>
+          <t>20876</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37858</t>
+          <t>38078</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45719</t>
+          <t>45204</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74294</t>
+          <t>74573</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14086</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17718</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -1069,97 +1069,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>515</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>515</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2082</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3343</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2766</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>140470</t>
+          <t>141214</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>162055</t>
+          <t>161817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138062</t>
+          <t>138375</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>156846</t>
+          <t>156261</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>285078</t>
+          <t>286349</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>314481</t>
+          <t>315081</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,6%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>14871</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34449</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16371</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30983</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35276</t>
+          <t>34916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59935</t>
+          <t>59892</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>9730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2111</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16589</t>
+          <t>17224</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5473</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2498</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>493</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -1863,17 +1863,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>144796</t>
+          <t>144795</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>49926</t>
+          <t>43488</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357980</t>
+          <t>360546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>66705</t>
+          <t>67038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74677</t>
+          <t>74757</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>81412</t>
+          <t>66707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>435554</t>
+          <t>434014</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>87,83%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43391</t>
+          <t>40573</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>364214</t>
+          <t>369713</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3501</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>10543</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>46224</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>409383</t>
+          <t>426646</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>86,34%</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16638</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3248</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>410</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15934</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,62 +2242,62 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>5966</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6024</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>391164</t>
+          <t>390648</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>421323</t>
+          <t>421352</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>276563</t>
+          <t>276440</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>299223</t>
+          <t>298685</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>676787</t>
+          <t>675009</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>714227</t>
+          <t>713567</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23182</t>
+          <t>22443</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>49229</t>
+          <t>51620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25477</t>
+          <t>26405</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44585</t>
+          <t>45740</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53943</t>
+          <t>53164</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86320</t>
+          <t>87379</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,01%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4340</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>17415</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16562</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>11683</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29904</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12107</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>10934</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18431</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>194269</t>
+          <t>194329</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>212381</t>
+          <t>212268</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>357698</t>
+          <t>357570</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>391028</t>
+          <t>389698</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>560510</t>
+          <t>562175</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>599041</t>
+          <t>595537</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25461</t>
+          <t>24978</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15148</t>
+          <t>14946</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39040</t>
+          <t>37997</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27159</t>
+          <t>27639</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>57519</t>
+          <t>55457</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1718</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2864</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12962</t>
+          <t>13137</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>13261</t>
+          <t>12956</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>6925</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>15117</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>17399</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>90513</t>
+          <t>90121</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>118180</t>
+          <t>117884</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>268243</t>
+          <t>268430</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>288220</t>
+          <t>288583</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>369301</t>
+          <t>365311</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>402392</t>
+          <t>401065</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2773</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26086</t>
+          <t>28527</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>18199</t>
+          <t>17547</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>36689</t>
+          <t>35229</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>24029</t>
+          <t>25289</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>50820</t>
+          <t>54404</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21602</t>
+          <t>17276</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7131</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17576</t>
+          <t>17772</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30161</t>
+          <t>30857</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>588</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5387</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>699191</t>
+          <t>740589</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1431346</t>
+          <t>1434036</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>45,68%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1320346</t>
+          <t>1321310</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1376792</t>
+          <t>1380510</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1947456</t>
+          <t>1936881</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2781222</t>
+          <t>2781206</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>145577</t>
+          <t>144011</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>898136</t>
+          <t>858302</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>55,39%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>122228</t>
+          <t>118677</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>166482</t>
+          <t>166602</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>288220</t>
+          <t>290292</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1152794</t>
+          <t>1165470</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,37%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>15545</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>47697</t>
+          <t>46103</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>27613</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>51666</t>
+          <t>51672</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>48886</t>
+          <t>49938</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>87136</t>
+          <t>90146</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17363</t>
+          <t>17559</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>12654</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>25981</t>
+          <t>26341</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>17883</t>
+          <t>18139</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>37681</t>
+          <t>37511</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21D6_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D6_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>189188</t>
+          <t>208450</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>174885</t>
+          <t>194362</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>199138</t>
+          <t>219133</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>186122</t>
+          <t>201455</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>176679</t>
+          <t>191694</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>194597</t>
+          <t>209693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>375310</t>
+          <t>409905</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>358708</t>
+          <t>392897</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>389290</t>
+          <t>424010</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>88,48%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29208</t>
+          <t>29232</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19279</t>
+          <t>19241</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42727</t>
+          <t>43293</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,22 +873,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28787</t>
+          <t>30357</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>22497</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38078</t>
+          <t>39836</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>57995</t>
+          <t>59588</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>45204</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74573</t>
+          <t>75954</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6728</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2655</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>16385</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2503</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>713</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>9072</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4499</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3101</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>510</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>152962</t>
+          <t>167330</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>141214</t>
+          <t>154871</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>161817</t>
+          <t>176755</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>148688</t>
+          <t>165252</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>138375</t>
+          <t>153934</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>156261</t>
+          <t>172777</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>301649</t>
+          <t>332582</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>286349</t>
+          <t>317073</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>315081</t>
+          <t>345179</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,71%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22883</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34525</t>
+          <t>34382</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22756</t>
+          <t>24965</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31121</t>
+          <t>33983</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>45639</t>
+          <t>47509</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34916</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59892</t>
+          <t>61410</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -1520,102 +1520,102 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>5542</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1695</t>
+          <t>2226</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9730</t>
+          <t>11119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>5,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>5879</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2136</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14045</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>11421</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>5648</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>21098</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,9%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>5,36%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6097</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>17224</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>10468</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>5474</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>20802</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1447</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1643,12 +1643,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>496</t>
+          <t>525</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -1678,12 +1678,12 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2498</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1943</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>523</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5602</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>144795</t>
+          <t>159518</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>43488</t>
+          <t>147939</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360546</t>
+          <t>169244</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>71390</t>
+          <t>78706</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67038</t>
+          <t>73617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74757</t>
+          <t>81855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>216186</t>
+          <t>238224</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66707</t>
+          <t>225342</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>434014</t>
+          <t>248681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>90,28%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>264430</t>
+          <t>23331</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40573</t>
+          <t>14661</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>369713</t>
+          <t>34151</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10543</t>
+          <t>11343</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>270986</t>
+          <t>30205</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>46224</t>
+          <t>21091</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>426646</t>
+          <t>42001</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -2089,67 +2089,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>4993</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12790</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1041</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16638</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,2%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>410</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>16798</t>
+          <t>12456</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>995</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2282,12 +2282,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>407931</t>
+          <t>458002</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>390648</t>
+          <t>438662</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>421352</t>
+          <t>472646</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>288409</t>
+          <t>331686</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>276440</t>
+          <t>318489</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>298685</t>
+          <t>342450</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>696339</t>
+          <t>789688</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>675009</t>
+          <t>768669</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>713567</t>
+          <t>809957</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>33240</t>
+          <t>37783</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22443</t>
+          <t>25726</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51620</t>
+          <t>56780</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>34866</t>
+          <t>37763</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26405</t>
+          <t>28434</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45740</t>
+          <t>49823</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>68106</t>
+          <t>75546</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53164</t>
+          <t>59619</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87379</t>
+          <t>95206</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>16788</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>18738</t>
+          <t>20889</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11683</t>
+          <t>13596</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>29431</t>
+          <t>32446</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6518</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3287</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10934</t>
+          <t>11758</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>10801</t>
+          <t>11375</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5437</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17734</t>
+          <t>18480</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>455229</t>
+          <t>510832</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>455229</t>
+          <t>510832</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>455229</t>
+          <t>510832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>338757</t>
+          <t>386666</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>793985</t>
+          <t>897498</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>793985</t>
+          <t>897498</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>793985</t>
+          <t>897498</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>205308</t>
+          <t>248404</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>194329</t>
+          <t>236506</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>212268</t>
+          <t>255647</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>371703</t>
+          <t>341189</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>357570</t>
+          <t>329685</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>389698</t>
+          <t>350886</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>577011</t>
+          <t>589594</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>562175</t>
+          <t>574091</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>595537</t>
+          <t>603236</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>14455</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>24978</t>
+          <t>26403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>28165</t>
+          <t>30354</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14946</t>
+          <t>22582</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37997</t>
+          <t>40707</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>42619</t>
+          <t>45685</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27639</t>
+          <t>34921</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>55457</t>
+          <t>60039</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13137</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12956</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3350,12 +3350,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>8948</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4640</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>10546</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>5521</t>
+          <t>5881</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>17399</t>
+          <t>16983</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>221071</t>
+          <t>265004</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>221071</t>
+          <t>265004</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>221071</t>
+          <t>265004</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>415856</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>636927</t>
+          <t>652885</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>636927</t>
+          <t>652885</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>636927</t>
+          <t>652885</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>108629</t>
+          <t>104095</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>90121</t>
+          <t>87971</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>117884</t>
+          <t>112240</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>279452</t>
+          <t>310161</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>268430</t>
+          <t>295761</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>288583</t>
+          <t>319831</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>388083</t>
+          <t>414256</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>365311</t>
+          <t>395954</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>401065</t>
+          <t>427770</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10582</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2672</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>23278</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>25285</t>
+          <t>29265</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>35229</t>
+          <t>41958</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>35867</t>
+          <t>39071</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>25289</t>
+          <t>28247</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>54404</t>
+          <t>57824</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,23%</t>
         </is>
       </c>
     </row>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3806,12 +3806,12 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>11680</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17772</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>16909</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>29879</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>618</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>6168</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,22 +3979,22 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>2339</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1208813</t>
+          <t>1345801</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>740589</t>
+          <t>1313082</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1434036</t>
+          <t>1373986</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>1345765</t>
+          <t>1428449</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1321310</t>
+          <t>1401362</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1380510</t>
+          <t>1451339</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>2554578</t>
+          <t>2774249</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1936881</t>
+          <t>2735692</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2781206</t>
+          <t>2811250</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>88,65%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>374798</t>
+          <t>138027</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>144011</t>
+          <t>112545</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>858302</t>
+          <t>168518</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>146414</t>
+          <t>159579</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>118677</t>
+          <t>140443</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>166602</t>
+          <t>183552</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>521212</t>
+          <t>297606</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>290292</t>
+          <t>264669</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1165470</t>
+          <t>333703</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>29217</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>15545</t>
+          <t>20820</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46103</t>
+          <t>47305</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,67 +4400,67 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>37868</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>27613</t>
+          <t>31620</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>51672</t>
+          <t>54445</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>71543</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>56601</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>91397</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
           <t>1,78%</t>
         </is>
       </c>
-      <c r="P36" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="R36" s="2" t="inlineStr">
-        <is>
-          <t>67086</t>
-        </is>
-      </c>
-      <c r="S36" s="2" t="inlineStr">
-        <is>
-          <t>49938</t>
-        </is>
-      </c>
-      <c r="T36" s="2" t="inlineStr">
-        <is>
-          <t>90146</t>
-        </is>
-      </c>
-      <c r="U36" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -4478,27 +4478,27 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>8597</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>16492</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>18261</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>13315</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>26341</t>
+          <t>27506</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>26859</t>
+          <t>27887</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>18139</t>
+          <t>19708</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>37511</t>
+          <t>39259</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>1621425</t>
+          <t>1523448</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1621425</t>
+          <t>1523448</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1621425</t>
+          <t>1523448</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1548309</t>
+          <t>1647837</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>1548309</t>
+          <t>1647837</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>1548309</t>
+          <t>1647837</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>3169734</t>
+          <t>3171284</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>3169734</t>
+          <t>3171284</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3169734</t>
+          <t>3171284</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
